--- a/0_OtrasTareas/trama etl vaope/Nomina/Datos Nomina.xlsx
+++ b/0_OtrasTareas/trama etl vaope/Nomina/Datos Nomina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOPORTE\Desktop\vaope-bi\0_OtrasTareas\trama etl vaope\Nomina\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64D648A-90FA-4306-A8CD-A118DB0E9A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4A1322-AD3E-4CD3-8DDD-F92263D408AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-1485" windowWidth="29040" windowHeight="15720" xr2:uid="{620EBC2B-9A86-4685-95E0-4E4DFA79EC74}"/>
   </bookViews>
@@ -35,8 +35,27 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FF23EC75-51D3-4436-A5A5-39D1DD7EAB09}</author>
+  </authors>
+  <commentList>
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{FF23EC75-51D3-4436-A5A5-39D1DD7EAB09}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Llega con formato cadena
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
     <t>NOMINA</t>
   </si>
@@ -183,6 +202,24 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Revisar si figura el nombre de la sede Surco, chorillos, remoto</t>
+  </si>
+  <si>
+    <t>Revisar si ingresan el dato</t>
+  </si>
+  <si>
+    <t>Falta agregar estos datos</t>
+  </si>
+  <si>
+    <t>Respuesta</t>
   </si>
 </sst>
 </file>
@@ -205,7 +242,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +252,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0504D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,12 +289,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -267,6 +311,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="u201823368 (Zuñiga Cordova, Johan Poul Hugo)" id="{7E4736BF-0F8E-49BE-8E4E-49B8D7F5680E}" userId="S::u201823368@upc.edu.pe::3056d3c3-15e3-4a3a-afaf-0258da932e9c" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,17 +634,28 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D19" dT="2025-10-29T14:30:15.22" personId="{7E4736BF-0F8E-49BE-8E4E-49B8D7F5680E}" id="{FF23EC75-51D3-4436-A5A5-39D1DD7EAB09}">
+    <text xml:space="preserve">Llega con formato cadena
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C788D3FE-8379-4BBB-A915-972AC0DB37AE}">
-  <dimension ref="B3:D24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C788D3FE-8379-4BBB-A915-972AC0DB37AE}">
+  <dimension ref="B3:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="70.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,8 +665,14 @@
       <c r="D3" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -615,8 +682,12 @@
       <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
@@ -626,8 +697,12 @@
       <c r="D5" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
@@ -637,8 +712,12 @@
       <c r="D6" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -648,8 +727,12 @@
       <c r="D7" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
@@ -659,8 +742,12 @@
       <c r="D8" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
@@ -670,8 +757,12 @@
       <c r="D9" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
@@ -681,8 +772,12 @@
       <c r="D10" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -692,8 +787,12 @@
       <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
@@ -703,8 +802,12 @@
       <c r="D12" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
@@ -714,8 +817,12 @@
       <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
@@ -725,8 +832,12 @@
       <c r="D14" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -736,8 +847,12 @@
       <c r="D15" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
@@ -747,8 +862,12 @@
       <c r="D16" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
@@ -758,8 +877,12 @@
       <c r="D17" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
@@ -769,19 +892,27 @@
       <c r="D18" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>21</v>
       </c>
@@ -791,8 +922,12 @@
       <c r="D20" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
@@ -802,8 +937,12 @@
       <c r="D21" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
@@ -813,8 +952,12 @@
       <c r="D22" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>41</v>
       </c>
@@ -824,8 +967,12 @@
       <c r="D23" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
@@ -835,8 +982,13 @@
       <c r="D24" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="E24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>